--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543293DC-BE26-4273-B8FF-8728FC340136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF3CA5D-C350-4813-A406-8CC1695B439F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
     <numFmt numFmtId="179" formatCode="yyyy\-m\-d"/>
     <numFmt numFmtId="180" formatCode="0.000000_);[Red]\(0.000000\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -88,13 +88,6 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -140,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -181,9 +174,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2000,6 +1990,9 @@
                 <c:pt idx="533">
                   <c:v>44742</c:v>
                 </c:pt>
+                <c:pt idx="534">
+                  <c:v>44743</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3610,6 +3603,9 @@
                 </c:pt>
                 <c:pt idx="533">
                   <c:v>1.7099260688446338</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>1.695446410968189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5294,6 +5290,9 @@
                 <c:pt idx="533">
                   <c:v>44742</c:v>
                 </c:pt>
+                <c:pt idx="534">
+                  <c:v>44743</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6904,6 +6903,9 @@
                 </c:pt>
                 <c:pt idx="533">
                   <c:v>1.1866235937814185</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>1.1817845085775367</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8796,6 +8798,9 @@
                 <c:pt idx="523">
                   <c:v>44742</c:v>
                 </c:pt>
+                <c:pt idx="524">
+                  <c:v>44743</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10376,6 +10381,9 @@
                 </c:pt>
                 <c:pt idx="523">
                   <c:v>1.7472861665357633</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>1.7282211368363916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11991,6 +11999,9 @@
                 <c:pt idx="523">
                   <c:v>44742</c:v>
                 </c:pt>
+                <c:pt idx="524">
+                  <c:v>44743</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13571,6 +13582,9 @@
                 </c:pt>
                 <c:pt idx="523">
                   <c:v>1.1872518291843586</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>1.1824101820184032</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -36039,7 +36053,44 @@
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E536" s="16"/>
+      <c r="A536" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B536" s="2">
+        <f t="shared" ref="B536" si="984">E536/F536</f>
+        <v>1.695446410968189</v>
+      </c>
+      <c r="C536" s="3">
+        <v>0</v>
+      </c>
+      <c r="D536" s="3">
+        <v>0</v>
+      </c>
+      <c r="E536" s="3">
+        <v>424411.41</v>
+      </c>
+      <c r="F536" s="3">
+        <f t="shared" ref="F536" si="985">F535+G536</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G536" s="3">
+        <f t="shared" ref="G536" si="986">(C536-D536)/((E536-C536+D536)/F535)</f>
+        <v>0</v>
+      </c>
+      <c r="H536" s="4">
+        <f t="shared" ref="H536" si="987">I536/J536</f>
+        <v>1.1817845085775367</v>
+      </c>
+      <c r="I536" s="5">
+        <v>4466.72</v>
+      </c>
+      <c r="J536" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K536" s="6">
+        <f t="shared" ref="K536" si="988">(B536-H536)</f>
+        <v>0.51366190239065235</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -36051,7 +36102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L525"/>
+  <dimension ref="A1:L526"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -57012,6 +57063,46 @@
         <v>0.56003433735140473</v>
       </c>
     </row>
+    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A526" s="1">
+        <v>44743</v>
+      </c>
+      <c r="B526" s="2">
+        <f t="shared" ref="B526" si="890">E526/F526</f>
+        <v>1.7282211368363916</v>
+      </c>
+      <c r="C526" s="3">
+        <v>0</v>
+      </c>
+      <c r="D526" s="3">
+        <v>0</v>
+      </c>
+      <c r="E526" s="3">
+        <v>809828.75</v>
+      </c>
+      <c r="F526" s="3">
+        <f t="shared" ref="F526" si="891">F525+G526</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G526" s="3">
+        <f t="shared" ref="G526" si="892">(C526-D526)/((E526-C526+D526)/F525)</f>
+        <v>0</v>
+      </c>
+      <c r="H526" s="4">
+        <f t="shared" ref="H526" si="893">I526/J526</f>
+        <v>1.1824101820184032</v>
+      </c>
+      <c r="I526" s="5">
+        <v>4466.72</v>
+      </c>
+      <c r="J526" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K526" s="6">
+        <f t="shared" ref="K526" si="894">(B526-H526)</f>
+        <v>0.54581095481798836</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF3CA5D-C350-4813-A406-8CC1695B439F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B67229B-8468-405F-AE0E-A2E33E336FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -1993,6 +1993,9 @@
                 <c:pt idx="534">
                   <c:v>44743</c:v>
                 </c:pt>
+                <c:pt idx="535">
+                  <c:v>44746</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3606,6 +3609,9 @@
                 </c:pt>
                 <c:pt idx="534">
                   <c:v>1.695446410968189</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>1.718488282466601</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5293,6 +5299,9 @@
                 <c:pt idx="534">
                   <c:v>44743</c:v>
                 </c:pt>
+                <c:pt idx="535">
+                  <c:v>44746</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6906,6 +6915,9 @@
                 </c:pt>
                 <c:pt idx="534">
                   <c:v>1.1817845085775367</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>1.1895392153750093</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7139,19 +7151,7 @@
               <a:rPr lang="zh-CN" altLang="zh-CN" sz="1800" b="0" i="0" baseline="0">
                 <a:effectLst/>
               </a:rPr>
-              <a:t>证券账户资产净值</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="zh-CN" altLang="en-US" sz="1800" b="0" i="0" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>月</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="zh-CN" altLang="zh-CN" sz="1800" b="0" i="0" baseline="0">
-                <a:effectLst/>
-              </a:rPr>
-              <a:t>走势图</a:t>
+              <a:t>证券账户资产净值走势图</a:t>
             </a:r>
             <a:endParaRPr lang="zh-CN" altLang="zh-CN">
               <a:effectLst/>
@@ -8801,6 +8801,9 @@
                 <c:pt idx="524">
                   <c:v>44743</c:v>
                 </c:pt>
+                <c:pt idx="525">
+                  <c:v>44746</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10384,6 +10387,9 @@
                 </c:pt>
                 <c:pt idx="524">
                   <c:v>1.7282211368363916</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>1.750912698529218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12002,6 +12008,9 @@
                 <c:pt idx="524">
                   <c:v>44743</c:v>
                 </c:pt>
+                <c:pt idx="525">
+                  <c:v>44746</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13585,6 +13594,9 @@
                 </c:pt>
                 <c:pt idx="524">
                   <c:v>1.1824101820184032</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>1.1901689943986191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14688,7 +14700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q536"/>
+  <dimension ref="A1:Q537"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36092,6 +36104,46 @@
         <v>0.51366190239065235</v>
       </c>
     </row>
+    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A537" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B537" s="2">
+        <f t="shared" ref="B537" si="989">E537/F537</f>
+        <v>1.718488282466601</v>
+      </c>
+      <c r="C537" s="3">
+        <v>0</v>
+      </c>
+      <c r="D537" s="3">
+        <v>0</v>
+      </c>
+      <c r="E537" s="3">
+        <v>430179.35</v>
+      </c>
+      <c r="F537" s="3">
+        <f t="shared" ref="F537" si="990">F536+G537</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G537" s="3">
+        <f t="shared" ref="G537" si="991">(C537-D537)/((E537-C537+D537)/F536)</f>
+        <v>0</v>
+      </c>
+      <c r="H537" s="4">
+        <f t="shared" ref="H537" si="992">I537/J537</f>
+        <v>1.1895392153750093</v>
+      </c>
+      <c r="I537" s="5">
+        <v>4496.03</v>
+      </c>
+      <c r="J537" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K537" s="6">
+        <f t="shared" ref="K537" si="993">(B537-H537)</f>
+        <v>0.52894906709159173</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36102,7 +36154,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L526"/>
+  <dimension ref="A1:L527"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -57103,6 +57155,46 @@
         <v>0.54581095481798836</v>
       </c>
     </row>
+    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A527" s="1">
+        <v>44746</v>
+      </c>
+      <c r="B527" s="2">
+        <f t="shared" ref="B527" si="895">E527/F527</f>
+        <v>1.750912698529218</v>
+      </c>
+      <c r="C527" s="3">
+        <v>0</v>
+      </c>
+      <c r="D527" s="3">
+        <v>0</v>
+      </c>
+      <c r="E527" s="3">
+        <v>820461.81</v>
+      </c>
+      <c r="F527" s="3">
+        <f t="shared" ref="F527" si="896">F526+G527</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G527" s="3">
+        <f t="shared" ref="G527" si="897">(C527-D527)/((E527-C527+D527)/F526)</f>
+        <v>0</v>
+      </c>
+      <c r="H527" s="4">
+        <f t="shared" ref="H527" si="898">I527/J527</f>
+        <v>1.1901689943986191</v>
+      </c>
+      <c r="I527" s="5">
+        <v>4496.03</v>
+      </c>
+      <c r="J527" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K527" s="6">
+        <f t="shared" ref="K527" si="899">(B527-H527)</f>
+        <v>0.56074370413059893</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B67229B-8468-405F-AE0E-A2E33E336FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1670C44-D17D-4964-BD1A-871DF6276009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -1996,6 +1996,9 @@
                 <c:pt idx="535">
                   <c:v>44746</c:v>
                 </c:pt>
+                <c:pt idx="536">
+                  <c:v>44747</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3612,6 +3615,9 @@
                 </c:pt>
                 <c:pt idx="535">
                   <c:v>1.718488282466601</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>1.7018543389972156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5302,6 +5308,9 @@
                 <c:pt idx="535">
                   <c:v>44746</c:v>
                 </c:pt>
+                <c:pt idx="536">
+                  <c:v>44747</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6918,6 +6927,9 @@
                 </c:pt>
                 <c:pt idx="535">
                   <c:v>1.1895392153750093</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>1.1878221206252448</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8804,6 +8816,9 @@
                 <c:pt idx="525">
                   <c:v>44746</c:v>
                 </c:pt>
+                <c:pt idx="526">
+                  <c:v>44747</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10390,6 +10405,9 @@
                 </c:pt>
                 <c:pt idx="525">
                   <c:v>1.750912698529218</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>1.7322766143921073</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12011,6 +12029,9 @@
                 <c:pt idx="525">
                   <c:v>44746</c:v>
                 </c:pt>
+                <c:pt idx="526">
+                  <c:v>44747</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13597,6 +13618,9 @@
                 </c:pt>
                 <c:pt idx="525">
                   <c:v>1.1901689943986191</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>1.1884509905655383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14700,7 +14724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q537"/>
+  <dimension ref="A1:Q538"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36144,6 +36168,46 @@
         <v>0.52894906709159173</v>
       </c>
     </row>
+    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A538" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B538" s="2">
+        <f t="shared" ref="B538" si="994">E538/F538</f>
+        <v>1.7018543389972156</v>
+      </c>
+      <c r="C538" s="3">
+        <v>0</v>
+      </c>
+      <c r="D538" s="3">
+        <v>0</v>
+      </c>
+      <c r="E538" s="3">
+        <v>426015.47</v>
+      </c>
+      <c r="F538" s="3">
+        <f t="shared" ref="F538" si="995">F537+G538</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G538" s="3">
+        <f t="shared" ref="G538" si="996">(C538-D538)/((E538-C538+D538)/F537)</f>
+        <v>0</v>
+      </c>
+      <c r="H538" s="4">
+        <f t="shared" ref="H538" si="997">I538/J538</f>
+        <v>1.1878221206252448</v>
+      </c>
+      <c r="I538" s="5">
+        <v>4489.54</v>
+      </c>
+      <c r="J538" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K538" s="6">
+        <f t="shared" ref="K538" si="998">(B538-H538)</f>
+        <v>0.51403221837197077</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36154,7 +36218,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L527"/>
+  <dimension ref="A1:L528"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -57195,6 +57259,46 @@
         <v>0.56074370413059893</v>
       </c>
     </row>
+    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A528" s="1">
+        <v>44747</v>
+      </c>
+      <c r="B528" s="2">
+        <f t="shared" ref="B528" si="900">E528/F528</f>
+        <v>1.7322766143921073</v>
+      </c>
+      <c r="C528" s="3">
+        <v>0</v>
+      </c>
+      <c r="D528" s="3">
+        <v>0</v>
+      </c>
+      <c r="E528" s="3">
+        <v>811729.11</v>
+      </c>
+      <c r="F528" s="3">
+        <f t="shared" ref="F528" si="901">F527+G528</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G528" s="3">
+        <f t="shared" ref="G528" si="902">(C528-D528)/((E528-C528+D528)/F527)</f>
+        <v>0</v>
+      </c>
+      <c r="H528" s="4">
+        <f t="shared" ref="H528" si="903">I528/J528</f>
+        <v>1.1884509905655383</v>
+      </c>
+      <c r="I528" s="5">
+        <v>4489.54</v>
+      </c>
+      <c r="J528" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K528" s="6">
+        <f t="shared" ref="K528" si="904">(B528-H528)</f>
+        <v>0.54382562382656907</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1670C44-D17D-4964-BD1A-871DF6276009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267D4A3E-DAF1-4B20-B982-560D5148AECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1999,6 +1999,9 @@
                 <c:pt idx="536">
                   <c:v>44747</c:v>
                 </c:pt>
+                <c:pt idx="537">
+                  <c:v>44748</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3618,6 +3621,9 @@
                 </c:pt>
                 <c:pt idx="536">
                   <c:v>1.7018543389972156</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>1.6637651859090041</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5311,6 +5317,9 @@
                 <c:pt idx="536">
                   <c:v>44747</c:v>
                 </c:pt>
+                <c:pt idx="537">
+                  <c:v>44748</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6930,6 +6939,9 @@
                 </c:pt>
                 <c:pt idx="536">
                   <c:v>1.1878221206252448</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>1.1704739075679167</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8819,6 +8831,9 @@
                 <c:pt idx="526">
                   <c:v>44747</c:v>
                 </c:pt>
+                <c:pt idx="527">
+                  <c:v>44748</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10408,6 +10423,9 @@
                 </c:pt>
                 <c:pt idx="526">
                   <c:v>1.7322766143921073</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>1.6929813169042791</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12032,6 +12050,9 @@
                 <c:pt idx="526">
                   <c:v>44747</c:v>
                 </c:pt>
+                <c:pt idx="527">
+                  <c:v>44748</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13621,6 +13642,9 @@
                 </c:pt>
                 <c:pt idx="526">
                   <c:v>1.1884509905655383</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>1.1710935928251502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14724,7 +14748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q538"/>
+  <dimension ref="A1:Q539"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36208,6 +36232,46 @@
         <v>0.51403221837197077</v>
       </c>
     </row>
+    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A539" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B539" s="2">
+        <f t="shared" ref="B539" si="999">E539/F539</f>
+        <v>1.6637651859090041</v>
+      </c>
+      <c r="C539" s="3">
+        <v>0</v>
+      </c>
+      <c r="D539" s="3">
+        <v>0</v>
+      </c>
+      <c r="E539" s="3">
+        <v>416480.83</v>
+      </c>
+      <c r="F539" s="3">
+        <f t="shared" ref="F539" si="1000">F538+G539</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G539" s="3">
+        <f t="shared" ref="G539" si="1001">(C539-D539)/((E539-C539+D539)/F538)</f>
+        <v>0</v>
+      </c>
+      <c r="H539" s="4">
+        <f t="shared" ref="H539" si="1002">I539/J539</f>
+        <v>1.1704739075679167</v>
+      </c>
+      <c r="I539" s="5">
+        <v>4423.97</v>
+      </c>
+      <c r="J539" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K539" s="6">
+        <f t="shared" ref="K539" si="1003">(B539-H539)</f>
+        <v>0.49329127834108744</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36218,7 +36282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L528"/>
+  <dimension ref="A1:L529"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -57299,6 +57363,46 @@
         <v>0.54382562382656907</v>
       </c>
     </row>
+    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A529" s="1">
+        <v>44748</v>
+      </c>
+      <c r="B529" s="2">
+        <f t="shared" ref="B529" si="905">E529/F529</f>
+        <v>1.6929813169042791</v>
+      </c>
+      <c r="C529" s="3">
+        <v>0</v>
+      </c>
+      <c r="D529" s="3">
+        <v>0</v>
+      </c>
+      <c r="E529" s="3">
+        <v>793315.69</v>
+      </c>
+      <c r="F529" s="3">
+        <f t="shared" ref="F529" si="906">F528+G529</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G529" s="3">
+        <f t="shared" ref="G529" si="907">(C529-D529)/((E529-C529+D529)/F528)</f>
+        <v>0</v>
+      </c>
+      <c r="H529" s="4">
+        <f t="shared" ref="H529" si="908">I529/J529</f>
+        <v>1.1710935928251502</v>
+      </c>
+      <c r="I529" s="5">
+        <v>4423.97</v>
+      </c>
+      <c r="J529" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K529" s="6">
+        <f t="shared" ref="K529" si="909">(B529-H529)</f>
+        <v>0.52188772407912887</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267D4A3E-DAF1-4B20-B982-560D5148AECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A38CE7-E739-4E94-BB26-DA9DFC0A0B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -2002,6 +2002,9 @@
                 <c:pt idx="537">
                   <c:v>44748</c:v>
                 </c:pt>
+                <c:pt idx="538">
+                  <c:v>44749</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3624,6 +3627,9 @@
                 </c:pt>
                 <c:pt idx="537">
                   <c:v>1.6637651859090041</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>1.654045593567681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5320,6 +5326,9 @@
                 <c:pt idx="537">
                   <c:v>44748</c:v>
                 </c:pt>
+                <c:pt idx="538">
+                  <c:v>44749</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6942,6 +6951,9 @@
                 </c:pt>
                 <c:pt idx="537">
                   <c:v>1.1704739075679167</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>1.1756331290810766</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8834,6 +8846,9 @@
                 <c:pt idx="527">
                   <c:v>44748</c:v>
                 </c:pt>
+                <c:pt idx="528">
+                  <c:v>44749</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10426,6 +10441,9 @@
                 </c:pt>
                 <c:pt idx="527">
                   <c:v>1.6929813169042791</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>1.6837957357862192</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12053,6 +12071,9 @@
                 <c:pt idx="527">
                   <c:v>44748</c:v>
                 </c:pt>
+                <c:pt idx="528">
+                  <c:v>44749</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13645,6 +13666,9 @@
                 </c:pt>
                 <c:pt idx="527">
                   <c:v>1.1710935928251502</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>1.1762555457904937</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14748,7 +14772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q539"/>
+  <dimension ref="A1:Q540"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36272,6 +36296,46 @@
         <v>0.49329127834108744</v>
       </c>
     </row>
+    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A540" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B540" s="2">
+        <f t="shared" ref="B540" si="1004">E540/F540</f>
+        <v>1.654045593567681</v>
+      </c>
+      <c r="C540" s="3">
+        <v>0</v>
+      </c>
+      <c r="D540" s="3">
+        <v>0</v>
+      </c>
+      <c r="E540" s="3">
+        <v>414047.78</v>
+      </c>
+      <c r="F540" s="3">
+        <f t="shared" ref="F540" si="1005">F539+G540</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G540" s="3">
+        <f t="shared" ref="G540" si="1006">(C540-D540)/((E540-C540+D540)/F539)</f>
+        <v>0</v>
+      </c>
+      <c r="H540" s="4">
+        <f t="shared" ref="H540" si="1007">I540/J540</f>
+        <v>1.1756331290810766</v>
+      </c>
+      <c r="I540" s="5">
+        <v>4443.47</v>
+      </c>
+      <c r="J540" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K540" s="6">
+        <f t="shared" ref="K540" si="1008">(B540-H540)</f>
+        <v>0.47841246448660435</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36282,7 +36346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L529"/>
+  <dimension ref="A1:L530"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -57403,6 +57467,46 @@
         <v>0.52188772407912887</v>
       </c>
     </row>
+    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A530" s="1">
+        <v>44749</v>
+      </c>
+      <c r="B530" s="2">
+        <f t="shared" ref="B530" si="910">E530/F530</f>
+        <v>1.6837957357862192</v>
+      </c>
+      <c r="C530" s="3">
+        <v>0</v>
+      </c>
+      <c r="D530" s="3">
+        <v>0</v>
+      </c>
+      <c r="E530" s="3">
+        <v>789011.41</v>
+      </c>
+      <c r="F530" s="3">
+        <f t="shared" ref="F530" si="911">F529+G530</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G530" s="3">
+        <f t="shared" ref="G530" si="912">(C530-D530)/((E530-C530+D530)/F529)</f>
+        <v>0</v>
+      </c>
+      <c r="H530" s="4">
+        <f t="shared" ref="H530" si="913">I530/J530</f>
+        <v>1.1762555457904937</v>
+      </c>
+      <c r="I530" s="5">
+        <v>4443.47</v>
+      </c>
+      <c r="J530" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K530" s="6">
+        <f t="shared" ref="K530" si="914">(B530-H530)</f>
+        <v>0.50754018999572548</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A38CE7-E739-4E94-BB26-DA9DFC0A0B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EDD11A-2E66-422B-B2C1-B49302AA41C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
     <numFmt numFmtId="179" formatCode="yyyy\-m\-d"/>
     <numFmt numFmtId="180" formatCode="0.000000_);[Red]\(0.000000\)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -88,6 +88,13 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -133,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -174,6 +181,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2005,6 +2015,9 @@
                 <c:pt idx="538">
                   <c:v>44749</c:v>
                 </c:pt>
+                <c:pt idx="539">
+                  <c:v>44750</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3630,6 +3643,9 @@
                 </c:pt>
                 <c:pt idx="538">
                   <c:v>1.654045593567681</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>1.6636176972222767</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5329,6 +5345,9 @@
                 <c:pt idx="538">
                   <c:v>44749</c:v>
                 </c:pt>
+                <c:pt idx="539">
+                  <c:v>44750</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6954,6 +6973,9 @@
                 </c:pt>
                 <c:pt idx="538">
                   <c:v>1.1756331290810766</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>1.1717465155411626</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8849,6 +8871,9 @@
                 <c:pt idx="528">
                   <c:v>44749</c:v>
                 </c:pt>
+                <c:pt idx="529">
+                  <c:v>44750</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10444,6 +10469,9 @@
                 </c:pt>
                 <c:pt idx="528">
                   <c:v>1.6837957357862192</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>1.6924743715395272</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12074,6 +12102,9 @@
                 <c:pt idx="528">
                   <c:v>44749</c:v>
                 </c:pt>
+                <c:pt idx="529">
+                  <c:v>44750</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13669,6 +13700,9 @@
                 </c:pt>
                 <c:pt idx="528">
                   <c:v>1.1762555457904937</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>1.1723668745566014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14772,7 +14806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q540"/>
+  <dimension ref="A1:Q542"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36336,6 +36370,49 @@
         <v>0.47841246448660435</v>
       </c>
     </row>
+    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A541" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B541" s="2">
+        <f t="shared" ref="B541" si="1009">E541/F541</f>
+        <v>1.6636176972222767</v>
+      </c>
+      <c r="C541" s="3">
+        <v>0</v>
+      </c>
+      <c r="D541" s="3">
+        <v>0</v>
+      </c>
+      <c r="E541" s="3">
+        <v>416443.91</v>
+      </c>
+      <c r="F541" s="3">
+        <f t="shared" ref="F541" si="1010">F540+G541</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G541" s="3">
+        <f t="shared" ref="G541" si="1011">(C541-D541)/((E541-C541+D541)/F540)</f>
+        <v>0</v>
+      </c>
+      <c r="H541" s="4">
+        <f t="shared" ref="H541" si="1012">I541/J541</f>
+        <v>1.1717465155411626</v>
+      </c>
+      <c r="I541" s="5">
+        <v>4428.78</v>
+      </c>
+      <c r="J541" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K541" s="6">
+        <f t="shared" ref="K541" si="1013">(B541-H541)</f>
+        <v>0.4918711816811141</v>
+      </c>
+    </row>
+    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E542" s="16"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36346,7 +36423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L530"/>
+  <dimension ref="A1:L531"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -57507,6 +57584,46 @@
         <v>0.50754018999572548</v>
       </c>
     </row>
+    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A531" s="1">
+        <v>44750</v>
+      </c>
+      <c r="B531" s="2">
+        <f t="shared" ref="B531" si="915">E531/F531</f>
+        <v>1.6924743715395272</v>
+      </c>
+      <c r="C531" s="3">
+        <v>0</v>
+      </c>
+      <c r="D531" s="3">
+        <v>0</v>
+      </c>
+      <c r="E531" s="3">
+        <v>793078.14</v>
+      </c>
+      <c r="F531" s="3">
+        <f t="shared" ref="F531" si="916">F530+G531</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G531" s="3">
+        <f t="shared" ref="G531" si="917">(C531-D531)/((E531-C531+D531)/F530)</f>
+        <v>0</v>
+      </c>
+      <c r="H531" s="4">
+        <f t="shared" ref="H531" si="918">I531/J531</f>
+        <v>1.1723668745566014</v>
+      </c>
+      <c r="I531" s="5">
+        <v>4428.78</v>
+      </c>
+      <c r="J531" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K531" s="6">
+        <f t="shared" ref="K531" si="919">(B531-H531)</f>
+        <v>0.5201074969829258</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94656D81-0F58-4250-BAD0-5BB72884F4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A269794-7288-4D39-B49F-8F904ABA52E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -75,8 +75,8 @@
     <numFmt numFmtId="176" formatCode="0.000000%"/>
     <numFmt numFmtId="177" formatCode="yyyy\-m\-d"/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="181" formatCode="0.000000_);[Red]\(0.000000\)"/>
-    <numFmt numFmtId="182" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="0.000000_);[Red]\(0.000000\)"/>
+    <numFmt numFmtId="180" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -141,10 +141,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -157,10 +157,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -169,11 +169,11 @@
     <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2014,6 +2014,9 @@
                 <c:pt idx="541">
                   <c:v>44754</c:v>
                 </c:pt>
+                <c:pt idx="542">
+                  <c:v>44755</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3648,6 +3651,9 @@
                 </c:pt>
                 <c:pt idx="541">
                   <c:v>1.6323987125732</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>1.6381045513093688</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5356,6 +5362,9 @@
                 <c:pt idx="541">
                   <c:v>44754</c:v>
                 </c:pt>
+                <c:pt idx="542">
+                  <c:v>44755</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6990,6 +6999,9 @@
                 </c:pt>
                 <c:pt idx="541">
                   <c:v>1.1412780053126752</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>1.1433522769364279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8894,6 +8906,9 @@
                 <c:pt idx="531">
                   <c:v>44754</c:v>
                 </c:pt>
+                <c:pt idx="532">
+                  <c:v>44755</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10498,6 +10513,9 @@
                 </c:pt>
                 <c:pt idx="531">
                   <c:v>1.6557500158316365</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>1.662870149375395</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12137,6 +12155,9 @@
                 <c:pt idx="531">
                   <c:v>44754</c:v>
                 </c:pt>
+                <c:pt idx="532">
+                  <c:v>44755</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13741,6 +13762,9 @@
                 </c:pt>
                 <c:pt idx="531">
                   <c:v>1.14188223335204</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>1.1439576031596448</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14844,7 +14868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q543"/>
+  <dimension ref="A1:Q544"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36528,17 +36552,57 @@
         <v>0.49112070726052481</v>
       </c>
     </row>
+    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A544" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B544" s="2">
+        <f t="shared" ref="B544" si="1019">E544/F544</f>
+        <v>1.6381045513093688</v>
+      </c>
+      <c r="C544" s="3">
+        <v>0</v>
+      </c>
+      <c r="D544" s="3">
+        <v>0</v>
+      </c>
+      <c r="E544" s="3">
+        <v>410057.35</v>
+      </c>
+      <c r="F544" s="3">
+        <f t="shared" ref="F544" si="1020">F543+G544</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G544" s="3">
+        <f t="shared" ref="G544" si="1021">(C544-D544)/((E544-C544+D544)/F543)</f>
+        <v>0</v>
+      </c>
+      <c r="H544" s="4">
+        <f t="shared" ref="H544" si="1022">I544/J544</f>
+        <v>1.1433522769364279</v>
+      </c>
+      <c r="I544" s="5">
+        <v>4321.46</v>
+      </c>
+      <c r="J544" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K544" s="6">
+        <f t="shared" ref="K544" si="1023">(B544-H544)</f>
+        <v>0.49475227437294089</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L533"/>
+  <dimension ref="A1:L534"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -57819,6 +57883,46 @@
         <v>0.51386778247959652</v>
       </c>
     </row>
+    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A534" s="1">
+        <v>44755</v>
+      </c>
+      <c r="B534" s="2">
+        <f t="shared" ref="B534" si="925">E534/F534</f>
+        <v>1.662870149375395</v>
+      </c>
+      <c r="C534" s="3">
+        <v>0</v>
+      </c>
+      <c r="D534" s="3">
+        <v>0</v>
+      </c>
+      <c r="E534" s="3">
+        <v>779205.87</v>
+      </c>
+      <c r="F534" s="3">
+        <f t="shared" ref="F534" si="926">F533+G534</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G534" s="3">
+        <f t="shared" ref="G534" si="927">(C534-D534)/((E534-C534+D534)/F533)</f>
+        <v>0</v>
+      </c>
+      <c r="H534" s="4">
+        <f t="shared" ref="H534" si="928">I534/J534</f>
+        <v>1.1439576031596448</v>
+      </c>
+      <c r="I534" s="5">
+        <v>4321.46</v>
+      </c>
+      <c r="J534" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K534" s="6">
+        <f t="shared" ref="K534" si="929">(B534-H534)</f>
+        <v>0.51891254621575023</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A269794-7288-4D39-B49F-8F904ABA52E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA14870-F643-42E3-9514-00C9E84BAE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -2017,6 +2017,9 @@
                 <c:pt idx="542">
                   <c:v>44755</c:v>
                 </c:pt>
+                <c:pt idx="543">
+                  <c:v>44756</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3654,6 +3657,9 @@
                 </c:pt>
                 <c:pt idx="542">
                   <c:v>1.6381045513093688</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>1.629619237937117</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5365,6 +5371,9 @@
                 <c:pt idx="542">
                   <c:v>44755</c:v>
                 </c:pt>
+                <c:pt idx="543">
+                  <c:v>44756</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7002,6 +7011,9 @@
                 </c:pt>
                 <c:pt idx="542">
                   <c:v>1.1433522769364279</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>1.1435136679683779</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8909,6 +8921,9 @@
                 <c:pt idx="532">
                   <c:v>44755</c:v>
                 </c:pt>
+                <c:pt idx="533">
+                  <c:v>44756</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10516,6 +10531,9 @@
                 </c:pt>
                 <c:pt idx="532">
                   <c:v>1.662870149375395</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>1.6579891970289413</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12158,6 +12176,9 @@
                 <c:pt idx="532">
                   <c:v>44755</c:v>
                 </c:pt>
+                <c:pt idx="533">
+                  <c:v>44756</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13765,6 +13786,9 @@
                 </c:pt>
                 <c:pt idx="532">
                   <c:v>1.1439576031596448</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>1.144119079637022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14868,7 +14892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q544"/>
+  <dimension ref="A1:Q545"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36592,6 +36616,46 @@
         <v>0.49475227437294089</v>
       </c>
     </row>
+    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A545" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B545" s="2">
+        <f t="shared" ref="B545" si="1024">E545/F545</f>
+        <v>1.629619237937117</v>
+      </c>
+      <c r="C545" s="3">
+        <v>0</v>
+      </c>
+      <c r="D545" s="3">
+        <v>0</v>
+      </c>
+      <c r="E545" s="3">
+        <v>407933.27</v>
+      </c>
+      <c r="F545" s="3">
+        <f t="shared" ref="F545" si="1025">F544+G545</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G545" s="3">
+        <f t="shared" ref="G545" si="1026">(C545-D545)/((E545-C545+D545)/F544)</f>
+        <v>0</v>
+      </c>
+      <c r="H545" s="4">
+        <f t="shared" ref="H545" si="1027">I545/J545</f>
+        <v>1.1435136679683779</v>
+      </c>
+      <c r="I545" s="5">
+        <v>4322.07</v>
+      </c>
+      <c r="J545" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K545" s="6">
+        <f t="shared" ref="K545" si="1028">(B545-H545)</f>
+        <v>0.4861055699687391</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36602,7 +36666,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L534"/>
+  <dimension ref="A1:L535"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -57901,15 +57965,15 @@
         <v>779205.87</v>
       </c>
       <c r="F534" s="3">
-        <f t="shared" ref="F534" si="926">F533+G534</f>
+        <f>F533+G534</f>
         <v>468590.93014128867</v>
       </c>
       <c r="G534" s="3">
-        <f t="shared" ref="G534" si="927">(C534-D534)/((E534-C534+D534)/F533)</f>
+        <f>(C534-D534)/((E534-C534+D534)/F533)</f>
         <v>0</v>
       </c>
       <c r="H534" s="4">
-        <f t="shared" ref="H534" si="928">I534/J534</f>
+        <f t="shared" ref="H534" si="926">I534/J534</f>
         <v>1.1439576031596448</v>
       </c>
       <c r="I534" s="5">
@@ -57919,8 +57983,48 @@
         <v>3777.64</v>
       </c>
       <c r="K534" s="6">
-        <f t="shared" ref="K534" si="929">(B534-H534)</f>
+        <f t="shared" ref="K534" si="927">(B534-H534)</f>
         <v>0.51891254621575023</v>
+      </c>
+    </row>
+    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A535" s="1">
+        <v>44756</v>
+      </c>
+      <c r="B535" s="2">
+        <f t="shared" ref="B535" si="928">E535/F535</f>
+        <v>1.6579891970289413</v>
+      </c>
+      <c r="C535" s="3">
+        <v>0</v>
+      </c>
+      <c r="D535" s="3">
+        <v>0</v>
+      </c>
+      <c r="E535" s="3">
+        <v>776918.7</v>
+      </c>
+      <c r="F535" s="3">
+        <f>F534+G535</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G535" s="3">
+        <f>(C535-D535)/((E535-C535+D535)/F534)</f>
+        <v>0</v>
+      </c>
+      <c r="H535" s="4">
+        <f t="shared" ref="H535" si="929">I535/J535</f>
+        <v>1.144119079637022</v>
+      </c>
+      <c r="I535" s="5">
+        <v>4322.07</v>
+      </c>
+      <c r="J535" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K535" s="6">
+        <f t="shared" ref="K535" si="930">(B535-H535)</f>
+        <v>0.51387011739191935</v>
       </c>
     </row>
   </sheetData>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA14870-F643-42E3-9514-00C9E84BAE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3563EF25-B347-451A-8CF1-08D59EAF1CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2020,6 +2020,9 @@
                 <c:pt idx="543">
                   <c:v>44756</c:v>
                 </c:pt>
+                <c:pt idx="544">
+                  <c:v>44757</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3660,6 +3663,9 @@
                 </c:pt>
                 <c:pt idx="543">
                   <c:v>1.629619237937117</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>1.6250413760585944</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5374,6 +5380,9 @@
                 <c:pt idx="543">
                   <c:v>44756</c:v>
                 </c:pt>
+                <c:pt idx="544">
+                  <c:v>44757</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7014,6 +7023,9 @@
                 </c:pt>
                 <c:pt idx="543">
                   <c:v>1.1435136679683779</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>1.1240567884772095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8924,6 +8936,9 @@
                 <c:pt idx="533">
                   <c:v>44756</c:v>
                 </c:pt>
+                <c:pt idx="534">
+                  <c:v>44757</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10534,6 +10549,9 @@
                 </c:pt>
                 <c:pt idx="533">
                   <c:v>1.6579891970289413</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>1.6532398946911242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12179,6 +12197,9 @@
                 <c:pt idx="533">
                   <c:v>44756</c:v>
                 </c:pt>
+                <c:pt idx="534">
+                  <c:v>44757</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13789,6 +13810,9 @@
                 </c:pt>
                 <c:pt idx="533">
                   <c:v>1.144119079637022</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>1.1246518990692602</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14892,7 +14916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q545"/>
+  <dimension ref="A1:Q546"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36656,6 +36680,46 @@
         <v>0.4861055699687391</v>
       </c>
     </row>
+    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A546" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B546" s="2">
+        <f t="shared" ref="B546" si="1029">E546/F546</f>
+        <v>1.6250413760585944</v>
+      </c>
+      <c r="C546" s="3">
+        <v>0</v>
+      </c>
+      <c r="D546" s="3">
+        <v>0</v>
+      </c>
+      <c r="E546" s="3">
+        <v>406787.32</v>
+      </c>
+      <c r="F546" s="3">
+        <f t="shared" ref="F546" si="1030">F545+G546</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G546" s="3">
+        <f t="shared" ref="G546" si="1031">(C546-D546)/((E546-C546+D546)/F545)</f>
+        <v>0</v>
+      </c>
+      <c r="H546" s="4">
+        <f t="shared" ref="H546" si="1032">I546/J546</f>
+        <v>1.1240567884772095</v>
+      </c>
+      <c r="I546" s="5">
+        <v>4248.53</v>
+      </c>
+      <c r="J546" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K546" s="6">
+        <f t="shared" ref="K546" si="1033">(B546-H546)</f>
+        <v>0.50098458758138498</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36666,7 +36730,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L535"/>
+  <dimension ref="A1:L536"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -58027,6 +58091,46 @@
         <v>0.51387011739191935</v>
       </c>
     </row>
+    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A536" s="1">
+        <v>44757</v>
+      </c>
+      <c r="B536" s="2">
+        <f t="shared" ref="B536" si="931">E536/F536</f>
+        <v>1.6532398946911242</v>
+      </c>
+      <c r="C536" s="3">
+        <v>0</v>
+      </c>
+      <c r="D536" s="3">
+        <v>0</v>
+      </c>
+      <c r="E536" s="3">
+        <v>774693.22</v>
+      </c>
+      <c r="F536" s="3">
+        <f>F535+G536</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G536" s="3">
+        <f>(C536-D536)/((E536-C536+D536)/F535)</f>
+        <v>0</v>
+      </c>
+      <c r="H536" s="4">
+        <f t="shared" ref="H536" si="932">I536/J536</f>
+        <v>1.1246518990692602</v>
+      </c>
+      <c r="I536" s="5">
+        <v>4248.53</v>
+      </c>
+      <c r="J536" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K536" s="6">
+        <f t="shared" ref="K536" si="933">(B536-H536)</f>
+        <v>0.52858799562186398</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3563EF25-B347-451A-8CF1-08D59EAF1CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF8BB9B-5E91-46A1-844B-37E39EAA114D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2023,6 +2023,9 @@
                 <c:pt idx="544">
                   <c:v>44757</c:v>
                 </c:pt>
+                <c:pt idx="545">
+                  <c:v>44760</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3666,6 +3669,9 @@
                 </c:pt>
                 <c:pt idx="544">
                   <c:v>1.6250413760585944</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>1.62588140642276</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5383,6 +5389,9 @@
                 <c:pt idx="544">
                   <c:v>44757</c:v>
                 </c:pt>
+                <c:pt idx="545">
+                  <c:v>44760</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7026,6 +7035,9 @@
                 </c:pt>
                 <c:pt idx="544">
                   <c:v>1.1240567884772095</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>1.1357139833423289</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8939,6 +8951,9 @@
                 <c:pt idx="534">
                   <c:v>44757</c:v>
                 </c:pt>
+                <c:pt idx="535">
+                  <c:v>44758</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10552,6 +10567,9 @@
                 </c:pt>
                 <c:pt idx="534">
                   <c:v>1.6532398946911242</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>1.6522477713483614</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12200,6 +12218,9 @@
                 <c:pt idx="534">
                   <c:v>44757</c:v>
                 </c:pt>
+                <c:pt idx="535">
+                  <c:v>44758</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13813,6 +13834,9 @@
                 </c:pt>
                 <c:pt idx="534">
                   <c:v>1.1246518990692602</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>1.1363152656155695</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14916,7 +14940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q546"/>
+  <dimension ref="A1:Q547"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36720,6 +36744,46 @@
         <v>0.50098458758138498</v>
       </c>
     </row>
+    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A547" s="1">
+        <v>44760</v>
+      </c>
+      <c r="B547" s="2">
+        <f t="shared" ref="B547" si="1034">E547/F547</f>
+        <v>1.62588140642276</v>
+      </c>
+      <c r="C547" s="3">
+        <v>0</v>
+      </c>
+      <c r="D547" s="3">
+        <v>0</v>
+      </c>
+      <c r="E547" s="3">
+        <v>406997.6</v>
+      </c>
+      <c r="F547" s="3">
+        <f t="shared" ref="F547" si="1035">F546+G547</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G547" s="3">
+        <f t="shared" ref="G547" si="1036">(C547-D547)/((E547-C547+D547)/F546)</f>
+        <v>0</v>
+      </c>
+      <c r="H547" s="4">
+        <f t="shared" ref="H547" si="1037">I547/J547</f>
+        <v>1.1357139833423289</v>
+      </c>
+      <c r="I547" s="5">
+        <v>4292.59</v>
+      </c>
+      <c r="J547" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K547" s="6">
+        <f t="shared" ref="K547" si="1038">(B547-H547)</f>
+        <v>0.49016742308043115</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36730,7 +36794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L536"/>
+  <dimension ref="A1:L537"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -58131,6 +58195,46 @@
         <v>0.52858799562186398</v>
       </c>
     </row>
+    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A537" s="1">
+        <v>44758</v>
+      </c>
+      <c r="B537" s="2">
+        <f t="shared" ref="B537" si="934">E537/F537</f>
+        <v>1.6522477713483614</v>
+      </c>
+      <c r="C537" s="3">
+        <v>0</v>
+      </c>
+      <c r="D537" s="3">
+        <v>0</v>
+      </c>
+      <c r="E537" s="3">
+        <v>774228.32</v>
+      </c>
+      <c r="F537" s="3">
+        <f>F536+G537</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G537" s="3">
+        <f>(C537-D537)/((E537-C537+D537)/F536)</f>
+        <v>0</v>
+      </c>
+      <c r="H537" s="4">
+        <f t="shared" ref="H537" si="935">I537/J537</f>
+        <v>1.1363152656155695</v>
+      </c>
+      <c r="I537" s="5">
+        <v>4292.59</v>
+      </c>
+      <c r="J537" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K537" s="6">
+        <f t="shared" ref="K537" si="936">(B537-H537)</f>
+        <v>0.51593250573279192</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF8BB9B-5E91-46A1-844B-37E39EAA114D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B137D00C-4D4E-4FA3-A52D-05F2D96A1629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -2026,6 +2026,9 @@
                 <c:pt idx="545">
                   <c:v>44760</c:v>
                 </c:pt>
+                <c:pt idx="546">
+                  <c:v>44761</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3672,6 +3675,9 @@
                 </c:pt>
                 <c:pt idx="545">
                   <c:v>1.62588140642276</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>1.6293573776062671</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5392,6 +5398,9 @@
                 <c:pt idx="545">
                   <c:v>44760</c:v>
                 </c:pt>
+                <c:pt idx="546">
+                  <c:v>44761</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7038,6 +7047,9 @@
                 </c:pt>
                 <c:pt idx="545">
                   <c:v>1.1357139833423289</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>1.1295573123366247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8952,7 +8964,10 @@
                   <c:v>44757</c:v>
                 </c:pt>
                 <c:pt idx="535">
-                  <c:v>44758</c:v>
+                  <c:v>44760</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>44761</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10570,6 +10585,9 @@
                 </c:pt>
                 <c:pt idx="535">
                   <c:v>1.6522477713483614</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>1.657786354861315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12219,7 +12237,10 @@
                   <c:v>44757</c:v>
                 </c:pt>
                 <c:pt idx="535">
-                  <c:v>44758</c:v>
+                  <c:v>44760</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>44761</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13837,6 +13858,9 @@
                 </c:pt>
                 <c:pt idx="535">
                   <c:v>1.1363152656155695</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>1.13016062938766</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14940,7 +14964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q547"/>
+  <dimension ref="A1:Q548"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36784,6 +36808,46 @@
         <v>0.49016742308043115</v>
       </c>
     </row>
+    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A548" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B548" s="2">
+        <f t="shared" ref="B548" si="1039">E548/F548</f>
+        <v>1.6293573776062671</v>
+      </c>
+      <c r="C548" s="3">
+        <v>0</v>
+      </c>
+      <c r="D548" s="3">
+        <v>0</v>
+      </c>
+      <c r="E548" s="3">
+        <v>407867.72</v>
+      </c>
+      <c r="F548" s="3">
+        <f t="shared" ref="F548" si="1040">F547+G548</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G548" s="3">
+        <f t="shared" ref="G548" si="1041">(C548-D548)/((E548-C548+D548)/F547)</f>
+        <v>0</v>
+      </c>
+      <c r="H548" s="4">
+        <f t="shared" ref="H548" si="1042">I548/J548</f>
+        <v>1.1295573123366247</v>
+      </c>
+      <c r="I548" s="5">
+        <v>4269.32</v>
+      </c>
+      <c r="J548" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K548" s="6">
+        <f t="shared" ref="K548" si="1043">(B548-H548)</f>
+        <v>0.49980006526964238</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36794,7 +36858,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L537"/>
+  <dimension ref="A1:L538"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -58197,7 +58261,7 @@
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A537" s="1">
-        <v>44758</v>
+        <v>44760</v>
       </c>
       <c r="B537" s="2">
         <f t="shared" ref="B537" si="934">E537/F537</f>
@@ -58233,6 +58297,46 @@
       <c r="K537" s="6">
         <f t="shared" ref="K537" si="936">(B537-H537)</f>
         <v>0.51593250573279192</v>
+      </c>
+    </row>
+    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A538" s="1">
+        <v>44761</v>
+      </c>
+      <c r="B538" s="2">
+        <f t="shared" ref="B538" si="937">E538/F538</f>
+        <v>1.657786354861315</v>
+      </c>
+      <c r="C538" s="3">
+        <v>0</v>
+      </c>
+      <c r="D538" s="3">
+        <v>0</v>
+      </c>
+      <c r="E538" s="3">
+        <v>776823.65</v>
+      </c>
+      <c r="F538" s="3">
+        <f>F537+G538</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G538" s="3">
+        <f>(C538-D538)/((E538-C538+D538)/F537)</f>
+        <v>0</v>
+      </c>
+      <c r="H538" s="4">
+        <f t="shared" ref="H538" si="938">I538/J538</f>
+        <v>1.13016062938766</v>
+      </c>
+      <c r="I538" s="5">
+        <v>4269.34</v>
+      </c>
+      <c r="J538" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K538" s="6">
+        <f t="shared" ref="K538" si="939">(B538-H538)</f>
+        <v>0.52762572547365494</v>
       </c>
     </row>
   </sheetData>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B137D00C-4D4E-4FA3-A52D-05F2D96A1629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC7C038-834E-45EB-AE5B-59667A0E30BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -2029,6 +2029,9 @@
                 <c:pt idx="546">
                   <c:v>44761</c:v>
                 </c:pt>
+                <c:pt idx="547">
+                  <c:v>44762</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3678,6 +3681,9 @@
                 </c:pt>
                 <c:pt idx="546">
                   <c:v>1.6293573776062671</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>1.6502212342918261</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5401,6 +5407,9 @@
                 <c:pt idx="546">
                   <c:v>44761</c:v>
                 </c:pt>
+                <c:pt idx="547">
+                  <c:v>44762</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7050,6 +7059,9 @@
                 </c:pt>
                 <c:pt idx="546">
                   <c:v>1.1295573123366247</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>1.1333883650294738</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8969,6 +8981,9 @@
                 <c:pt idx="536">
                   <c:v>44761</c:v>
                 </c:pt>
+                <c:pt idx="537">
+                  <c:v>44762</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10588,6 +10603,9 @@
                 </c:pt>
                 <c:pt idx="536">
                   <c:v>1.657786354861315</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>1.6842114288512584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12242,6 +12260,9 @@
                 <c:pt idx="536">
                   <c:v>44761</c:v>
                 </c:pt>
+                <c:pt idx="537">
+                  <c:v>44762</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13861,6 +13882,9 @@
                 </c:pt>
                 <c:pt idx="536">
                   <c:v>1.13016062938766</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>1.1339884160481148</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14964,7 +14988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q548"/>
+  <dimension ref="A1:Q549"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -36848,6 +36872,46 @@
         <v>0.49980006526964238</v>
       </c>
     </row>
+    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A549" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B549" s="2">
+        <f t="shared" ref="B549" si="1044">E549/F549</f>
+        <v>1.6502212342918261</v>
+      </c>
+      <c r="C549" s="3">
+        <v>0</v>
+      </c>
+      <c r="D549" s="3">
+        <v>0</v>
+      </c>
+      <c r="E549" s="3">
+        <v>413090.45</v>
+      </c>
+      <c r="F549" s="3">
+        <f t="shared" ref="F549" si="1045">F548+G549</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G549" s="3">
+        <f t="shared" ref="G549" si="1046">(C549-D549)/((E549-C549+D549)/F548)</f>
+        <v>0</v>
+      </c>
+      <c r="H549" s="4">
+        <f t="shared" ref="H549" si="1047">I549/J549</f>
+        <v>1.1333883650294738</v>
+      </c>
+      <c r="I549" s="5">
+        <v>4283.8</v>
+      </c>
+      <c r="J549" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K549" s="6">
+        <f t="shared" ref="K549" si="1048">(B549-H549)</f>
+        <v>0.51683286926235228</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -36858,7 +36922,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L538"/>
+  <dimension ref="A1:L539"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -58339,6 +58403,46 @@
         <v>0.52762572547365494</v>
       </c>
     </row>
+    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A539" s="1">
+        <v>44762</v>
+      </c>
+      <c r="B539" s="2">
+        <f t="shared" ref="B539" si="940">E539/F539</f>
+        <v>1.6842114288512584</v>
+      </c>
+      <c r="C539" s="3">
+        <v>0</v>
+      </c>
+      <c r="D539" s="3">
+        <v>0</v>
+      </c>
+      <c r="E539" s="3">
+        <v>789206.2</v>
+      </c>
+      <c r="F539" s="3">
+        <f>F538+G539</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G539" s="3">
+        <f>(C539-D539)/((E539-C539+D539)/F538)</f>
+        <v>0</v>
+      </c>
+      <c r="H539" s="4">
+        <f t="shared" ref="H539" si="941">I539/J539</f>
+        <v>1.1339884160481148</v>
+      </c>
+      <c r="I539" s="5">
+        <v>4283.8</v>
+      </c>
+      <c r="J539" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K539" s="6">
+        <f t="shared" ref="K539" si="942">(B539-H539)</f>
+        <v>0.55022301280314356</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B075F36-B83D-45CB-8E95-0538252CF6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9327CFE-36C8-4BE9-BD48-E99461A14E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="465" windowWidth="28800" windowHeight="14685" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -75,8 +75,8 @@
     <numFmt numFmtId="176" formatCode="0.000000%"/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.000000_);[Red]\(0.000000\)"/>
-    <numFmt numFmtId="180" formatCode="0.00_ "/>
-    <numFmt numFmtId="182" formatCode="yyyy\-m\-d"/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="180" formatCode="yyyy\-m\-d"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -135,13 +135,13 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -151,13 +151,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -169,11 +169,11 @@
     <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2038,6 +2038,9 @@
                 <c:pt idx="549">
                   <c:v>44764</c:v>
                 </c:pt>
+                <c:pt idx="550">
+                  <c:v>44767</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3696,6 +3699,9 @@
                 </c:pt>
                 <c:pt idx="549">
                   <c:v>1.6166890501831233</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>1.6290259674911294</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5428,6 +5434,9 @@
                 <c:pt idx="549">
                   <c:v>44764</c:v>
                 </c:pt>
+                <c:pt idx="550">
+                  <c:v>44767</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7086,6 +7095,9 @@
                 </c:pt>
                 <c:pt idx="549">
                   <c:v>1.1213316612164121</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>1.1145611751383731</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9014,6 +9026,9 @@
                 <c:pt idx="539">
                   <c:v>44764</c:v>
                 </c:pt>
+                <c:pt idx="540">
+                  <c:v>44767</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10642,6 +10657,9 @@
                 </c:pt>
                 <c:pt idx="539">
                   <c:v>1.6484952019175581</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>1.6609308672818941</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12305,6 +12323,9 @@
                 <c:pt idx="539">
                   <c:v>44764</c:v>
                 </c:pt>
+                <c:pt idx="540">
+                  <c:v>44767</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13933,6 +13954,9 @@
                 </c:pt>
                 <c:pt idx="539">
                   <c:v>1.121925329041412</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>1.1151512584576615</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15036,7 +15060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q551"/>
+  <dimension ref="A1:Q552"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -37040,17 +37064,57 @@
         <v>0.49535738896671111</v>
       </c>
     </row>
+    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A552" s="1">
+        <v>44767</v>
+      </c>
+      <c r="B552" s="2">
+        <f t="shared" ref="B552" si="1054">E552/F552</f>
+        <v>1.6290259674911294</v>
+      </c>
+      <c r="C552" s="3">
+        <v>0</v>
+      </c>
+      <c r="D552" s="3">
+        <v>0</v>
+      </c>
+      <c r="E552" s="3">
+        <v>407784.76</v>
+      </c>
+      <c r="F552" s="3">
+        <f t="shared" ref="F552" si="1055">F551+G552</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G552" s="3">
+        <f t="shared" ref="G552" si="1056">(C552-D552)/((E552-C552+D552)/F551)</f>
+        <v>0</v>
+      </c>
+      <c r="H552" s="4">
+        <f t="shared" ref="H552" si="1057">I552/J552</f>
+        <v>1.1145611751383731</v>
+      </c>
+      <c r="I552" s="5">
+        <v>4212.6400000000003</v>
+      </c>
+      <c r="J552" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K552" s="6">
+        <f t="shared" ref="K552" si="1058">(B552-H552)</f>
+        <v>0.51446479235275633</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L541"/>
+  <dimension ref="A1:L542"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -58651,6 +58715,46 @@
         <v>0.52656987287614609</v>
       </c>
     </row>
+    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A542" s="1">
+        <v>44767</v>
+      </c>
+      <c r="B542" s="2">
+        <f t="shared" ref="B542" si="948">E542/F542</f>
+        <v>1.6609308672818941</v>
+      </c>
+      <c r="C542" s="3">
+        <v>0</v>
+      </c>
+      <c r="D542" s="3">
+        <v>0</v>
+      </c>
+      <c r="E542" s="3">
+        <v>778297.14</v>
+      </c>
+      <c r="F542" s="3">
+        <f t="shared" ref="F542" si="949">F541+G542</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G542" s="3">
+        <f t="shared" ref="G542" si="950">(C542-D542)/((E542-C542+D542)/F541)</f>
+        <v>0</v>
+      </c>
+      <c r="H542" s="4">
+        <f t="shared" ref="H542" si="951">I542/J542</f>
+        <v>1.1151512584576615</v>
+      </c>
+      <c r="I542" s="5">
+        <v>4212.6400000000003</v>
+      </c>
+      <c r="J542" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K542" s="6">
+        <f t="shared" ref="K542" si="952">(B542-H542)</f>
+        <v>0.5457796088242326</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9327CFE-36C8-4BE9-BD48-E99461A14E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55456ECC-D60F-46F6-9409-1D6305633A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="个人账户" sheetId="1" r:id="rId1"/>
@@ -2041,6 +2041,9 @@
                 <c:pt idx="550">
                   <c:v>44767</c:v>
                 </c:pt>
+                <c:pt idx="551">
+                  <c:v>44768</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3702,6 +3705,9 @@
                 </c:pt>
                 <c:pt idx="550">
                   <c:v>1.6290259674911294</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>1.6365767730495651</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5437,6 +5443,9 @@
                 <c:pt idx="550">
                   <c:v>44767</c:v>
                 </c:pt>
+                <c:pt idx="551">
+                  <c:v>44768</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7098,6 +7107,9 @@
                 </c:pt>
                 <c:pt idx="550">
                   <c:v>1.1145611751383731</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>1.1233821210485655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9029,6 +9041,9 @@
                 <c:pt idx="540">
                   <c:v>44767</c:v>
                 </c:pt>
+                <c:pt idx="541">
+                  <c:v>44768</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10660,6 +10675,9 @@
                 </c:pt>
                 <c:pt idx="540">
                   <c:v>1.6609308672818941</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>1.6696422821587658</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12326,6 +12344,9 @@
                 <c:pt idx="540">
                   <c:v>44767</c:v>
                 </c:pt>
+                <c:pt idx="541">
+                  <c:v>44768</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13957,6 +13978,9 @@
                 </c:pt>
                 <c:pt idx="540">
                   <c:v>1.1151512584576615</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>1.1239768744507153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15060,7 +15084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q552"/>
+  <dimension ref="A1:Q553"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -37104,6 +37128,46 @@
         <v>0.51446479235275633</v>
       </c>
     </row>
+    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A553" s="1">
+        <v>44768</v>
+      </c>
+      <c r="B553" s="2">
+        <f t="shared" ref="B553" si="1059">E553/F553</f>
+        <v>1.6365767730495651</v>
+      </c>
+      <c r="C553" s="3">
+        <v>0</v>
+      </c>
+      <c r="D553" s="3">
+        <v>0</v>
+      </c>
+      <c r="E553" s="3">
+        <v>409674.91</v>
+      </c>
+      <c r="F553" s="3">
+        <f t="shared" ref="F553" si="1060">F552+G553</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G553" s="3">
+        <f t="shared" ref="G553" si="1061">(C553-D553)/((E553-C553+D553)/F552)</f>
+        <v>0</v>
+      </c>
+      <c r="H553" s="4">
+        <f t="shared" ref="H553" si="1062">I553/J553</f>
+        <v>1.1233821210485655</v>
+      </c>
+      <c r="I553" s="5">
+        <v>4245.9799999999996</v>
+      </c>
+      <c r="J553" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K553" s="6">
+        <f t="shared" ref="K553" si="1063">(B553-H553)</f>
+        <v>0.51319465200099956</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -37114,7 +37178,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L542"/>
+  <dimension ref="A1:L543"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -58755,6 +58819,46 @@
         <v>0.5457796088242326</v>
       </c>
     </row>
+    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A543" s="1">
+        <v>44768</v>
+      </c>
+      <c r="B543" s="2">
+        <f t="shared" ref="B543" si="953">E543/F543</f>
+        <v>1.6696422821587658</v>
+      </c>
+      <c r="C543" s="3">
+        <v>0</v>
+      </c>
+      <c r="D543" s="3">
+        <v>0</v>
+      </c>
+      <c r="E543" s="3">
+        <v>782379.23</v>
+      </c>
+      <c r="F543" s="3">
+        <f t="shared" ref="F543" si="954">F542+G543</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G543" s="3">
+        <f t="shared" ref="G543" si="955">(C543-D543)/((E543-C543+D543)/F542)</f>
+        <v>0</v>
+      </c>
+      <c r="H543" s="4">
+        <f t="shared" ref="H543" si="956">I543/J543</f>
+        <v>1.1239768744507153</v>
+      </c>
+      <c r="I543" s="5">
+        <v>4245.9799999999996</v>
+      </c>
+      <c r="J543" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K543" s="6">
+        <f t="shared" ref="K543" si="957">(B543-H543)</f>
+        <v>0.5456654077080505</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55456ECC-D60F-46F6-9409-1D6305633A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1554519-E1CB-4B19-BC09-BE05924A2585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2044,6 +2044,9 @@
                 <c:pt idx="551">
                   <c:v>44768</c:v>
                 </c:pt>
+                <c:pt idx="552">
+                  <c:v>44769</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3708,6 +3711,9 @@
                 </c:pt>
                 <c:pt idx="551">
                   <c:v>1.6365767730495651</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>1.6277367997204431</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5446,6 +5452,9 @@
                 <c:pt idx="551">
                   <c:v>44768</c:v>
                 </c:pt>
+                <c:pt idx="552">
+                  <c:v>44769</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7110,6 +7119,9 @@
                 </c:pt>
                 <c:pt idx="551">
                   <c:v>1.1233821210485655</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>1.1178419108698183</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9044,6 +9056,9 @@
                 <c:pt idx="541">
                   <c:v>44768</c:v>
                 </c:pt>
+                <c:pt idx="542">
+                  <c:v>44769</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10678,6 +10693,9 @@
                 </c:pt>
                 <c:pt idx="541">
                   <c:v>1.6696422821587658</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>1.659915013219468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12347,6 +12365,9 @@
                 <c:pt idx="541">
                   <c:v>44768</c:v>
                 </c:pt>
+                <c:pt idx="542">
+                  <c:v>44769</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13981,6 +14002,9 @@
                 </c:pt>
                 <c:pt idx="541">
                   <c:v>1.1239768744507153</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>1.1184337311125465</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15084,7 +15108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q553"/>
+  <dimension ref="A1:Q554"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -37168,6 +37192,46 @@
         <v>0.51319465200099956</v>
       </c>
     </row>
+    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A554" s="1">
+        <v>44769</v>
+      </c>
+      <c r="B554" s="2">
+        <f t="shared" ref="B554" si="1064">E554/F554</f>
+        <v>1.6277367997204431</v>
+      </c>
+      <c r="C554" s="3">
+        <v>0</v>
+      </c>
+      <c r="D554" s="3">
+        <v>0</v>
+      </c>
+      <c r="E554" s="3">
+        <v>407462.05</v>
+      </c>
+      <c r="F554" s="3">
+        <f t="shared" ref="F554" si="1065">F553+G554</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G554" s="3">
+        <f t="shared" ref="G554" si="1066">(C554-D554)/((E554-C554+D554)/F553)</f>
+        <v>0</v>
+      </c>
+      <c r="H554" s="4">
+        <f t="shared" ref="H554" si="1067">I554/J554</f>
+        <v>1.1178419108698183</v>
+      </c>
+      <c r="I554" s="5">
+        <v>4225.04</v>
+      </c>
+      <c r="J554" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K554" s="6">
+        <f t="shared" ref="K554" si="1068">(B554-H554)</f>
+        <v>0.50989488885062473</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -37178,7 +37242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L543"/>
+  <dimension ref="A1:L544"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -58859,6 +58923,46 @@
         <v>0.5456654077080505</v>
       </c>
     </row>
+    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A544" s="1">
+        <v>44769</v>
+      </c>
+      <c r="B544" s="2">
+        <f t="shared" ref="B544" si="958">E544/F544</f>
+        <v>1.659915013219468</v>
+      </c>
+      <c r="C544" s="3">
+        <v>0</v>
+      </c>
+      <c r="D544" s="3">
+        <v>0</v>
+      </c>
+      <c r="E544" s="3">
+        <v>777821.12</v>
+      </c>
+      <c r="F544" s="3">
+        <f t="shared" ref="F544" si="959">F543+G544</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G544" s="3">
+        <f t="shared" ref="G544" si="960">(C544-D544)/((E544-C544+D544)/F543)</f>
+        <v>0</v>
+      </c>
+      <c r="H544" s="4">
+        <f t="shared" ref="H544" si="961">I544/J544</f>
+        <v>1.1184337311125465</v>
+      </c>
+      <c r="I544" s="5">
+        <v>4225.04</v>
+      </c>
+      <c r="J544" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K544" s="6">
+        <f t="shared" ref="K544" si="962">(B544-H544)</f>
+        <v>0.54148128210692148</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>

--- a/净值.xlsx
+++ b/净值.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\finance\recording\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1554519-E1CB-4B19-BC09-BE05924A2585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B07525A-15BD-4D86-91F2-F463F65D1AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="285" windowWidth="29040" windowHeight="15615" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2047,6 +2047,9 @@
                 <c:pt idx="552">
                   <c:v>44769</c:v>
                 </c:pt>
+                <c:pt idx="553">
+                  <c:v>44770</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3714,6 +3717,9 @@
                 </c:pt>
                 <c:pt idx="552">
                   <c:v>1.6277367997204431</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>1.6275445291220632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5455,6 +5461,9 @@
                 <c:pt idx="552">
                   <c:v>44769</c:v>
                 </c:pt>
+                <c:pt idx="553">
+                  <c:v>44770</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7122,6 +7131,9 @@
                 </c:pt>
                 <c:pt idx="552">
                   <c:v>1.1178419108698183</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>1.1180085934110127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9059,6 +9071,9 @@
                 <c:pt idx="542">
                   <c:v>44769</c:v>
                 </c:pt>
+                <c:pt idx="543">
+                  <c:v>44770</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10696,6 +10711,9 @@
                 </c:pt>
                 <c:pt idx="542">
                   <c:v>1.659915013219468</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>1.6606657533157263</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12368,6 +12386,9 @@
                 <c:pt idx="542">
                   <c:v>44769</c:v>
                 </c:pt>
+                <c:pt idx="543">
+                  <c:v>44770</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14005,6 +14026,9 @@
                 </c:pt>
                 <c:pt idx="542">
                   <c:v>1.1184337311125465</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>1.1186005019006575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15108,7 +15132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q554"/>
+  <dimension ref="A1:Q555"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -37232,6 +37256,46 @@
         <v>0.50989488885062473</v>
       </c>
     </row>
+    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A555" s="1">
+        <v>44770</v>
+      </c>
+      <c r="B555" s="2">
+        <f t="shared" ref="B555" si="1069">E555/F555</f>
+        <v>1.6275445291220632</v>
+      </c>
+      <c r="C555" s="3">
+        <v>0</v>
+      </c>
+      <c r="D555" s="3">
+        <v>0</v>
+      </c>
+      <c r="E555" s="3">
+        <v>407413.92</v>
+      </c>
+      <c r="F555" s="3">
+        <f t="shared" ref="F555" si="1070">F554+G555</f>
+        <v>250324.28465706488</v>
+      </c>
+      <c r="G555" s="3">
+        <f t="shared" ref="G555" si="1071">(C555-D555)/((E555-C555+D555)/F554)</f>
+        <v>0</v>
+      </c>
+      <c r="H555" s="4">
+        <f t="shared" ref="H555" si="1072">I555/J555</f>
+        <v>1.1180085934110127</v>
+      </c>
+      <c r="I555" s="5">
+        <v>4225.67</v>
+      </c>
+      <c r="J555" s="5">
+        <v>3779.64</v>
+      </c>
+      <c r="K555" s="6">
+        <f t="shared" ref="K555" si="1073">(B555-H555)</f>
+        <v>0.50953593571105049</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
@@ -37242,7 +37306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L544"/>
+  <dimension ref="A1:L545"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" style="1" customWidth="1"/>
@@ -58963,6 +59027,46 @@
         <v>0.54148128210692148</v>
       </c>
     </row>
+    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A545" s="1">
+        <v>44770</v>
+      </c>
+      <c r="B545" s="2">
+        <f t="shared" ref="B545" si="963">E545/F545</f>
+        <v>1.6606657533157263</v>
+      </c>
+      <c r="C545" s="3">
+        <v>0</v>
+      </c>
+      <c r="D545" s="3">
+        <v>0</v>
+      </c>
+      <c r="E545" s="3">
+        <v>778172.91</v>
+      </c>
+      <c r="F545" s="3">
+        <f t="shared" ref="F545" si="964">F544+G545</f>
+        <v>468590.93014128867</v>
+      </c>
+      <c r="G545" s="3">
+        <f t="shared" ref="G545" si="965">(C545-D545)/((E545-C545+D545)/F544)</f>
+        <v>0</v>
+      </c>
+      <c r="H545" s="4">
+        <f t="shared" ref="H545" si="966">I545/J545</f>
+        <v>1.1186005019006575</v>
+      </c>
+      <c r="I545" s="5">
+        <v>4225.67</v>
+      </c>
+      <c r="J545" s="5">
+        <v>3777.64</v>
+      </c>
+      <c r="K545" s="6">
+        <f t="shared" ref="K545" si="967">(B545-H545)</f>
+        <v>0.54206525141506878</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
